--- a/week4/homework-step-functions-trees.xlsx
+++ b/week4/homework-step-functions-trees.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="134">
   <si>
     <t xml:space="preserve">[Description] Step Functions &amp; Trees</t>
   </si>
@@ -153,6 +153,9 @@
     <t xml:space="preserve">which bin is it in?</t>
   </si>
   <si>
+    <t xml:space="preserve">Your Answer:</t>
+  </si>
+  <si>
     <t xml:space="preserve">[Description] STEP 2: find the best first split of a regression tree</t>
   </si>
   <si>
@@ -375,7 +378,7 @@
     <t xml:space="preserve">Total RSS by s=1.5..5.5</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8, 5.5, 22.67, 31, 50.8</t>
+    <t xml:space="preserve">38.8, 5.5, 22.67, 37.5, 53.2</t>
   </si>
   <si>
     <t xml:space="preserve">Best split</t>
@@ -1047,7 +1050,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -1207,20 +1210,22 @@
       <c r="A26" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C26" s="11" t="s">
+      <c r="D26" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="D26" s="11"/>
       <c r="E26" s="11"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="5" t="str">
-        <f aca="false">IF(F26="","",IF(ROUND(F26,3)=ROUND(14,3),"✓","✗"))</f>
+      <c r="F26" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G26" s="12"/>
+      <c r="H26" s="5" t="str">
+        <f aca="false">IF(G26="","",IF(ROUND(G26,3)=ROUND(14,3),"✓","✗"))</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="D26:E26"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:J26">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
@@ -1245,7 +1250,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
@@ -1256,17 +1261,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1353,27 +1358,27 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G19" s="10" t="s">
         <v>36</v>
@@ -1389,7 +1394,7 @@
       <c r="E20" s="8"/>
       <c r="F20" s="8"/>
       <c r="G20" s="5" t="str">
-        <f aca="false">IF(COUNT(B20:F20)=0,"",IF(AND(ROUND(B20,3)=ROUND(2,3),ROUND(C20,3)=ROUND(8.2,3),ROUND(D20,3)=ROUND(0,3),ROUND(E20,3)=ROUND(6.8,3),ROUND(F20,3)=ROUND(6.8,3)),"✓","✗"))</f>
+        <f aca="false">IF(COUNT(B20:F20)=0,"",IF(AND(ROUND(B20,3)=ROUND(2,3),ROUND(C20,3)=ROUND(8.2,3),ROUND(D20,3)=ROUND(0,3),ROUND(E20,3)=ROUND(38.8,3),ROUND(F20,3)=ROUND(38.8,3)),"✓","✗"))</f>
         <v/>
       </c>
     </row>
@@ -1431,7 +1436,7 @@
       <c r="E23" s="8"/>
       <c r="F23" s="8"/>
       <c r="G23" s="5" t="str">
-        <f aca="false">IF(COUNT(B23:F23)=0,"",IF(AND(ROUND(B23,3)=ROUND(5.5,3),ROUND(C23,3)=ROUND(10.5,3),ROUND(D23,3)=ROUND(29,3),ROUND(E23,3)=ROUND(2,3),ROUND(F23,3)=ROUND(31,3)),"✓","✗"))</f>
+        <f aca="false">IF(COUNT(B23:F23)=0,"",IF(AND(ROUND(B23,3)=ROUND(5.5,3),ROUND(C23,3)=ROUND(10.5,3),ROUND(D23,3)=ROUND(37,3),ROUND(E23,3)=ROUND(0.5,3),ROUND(F23,3)=ROUND(37.5,3)),"✓","✗"))</f>
         <v/>
       </c>
     </row>
@@ -1445,56 +1450,62 @@
       <c r="E24" s="8"/>
       <c r="F24" s="8"/>
       <c r="G24" s="5" t="str">
-        <f aca="false">IF(COUNT(B24:F24)=0,"",IF(AND(ROUND(B24,3)=ROUND(6.4,3),ROUND(C24,3)=ROUND(11,3),ROUND(D24,3)=ROUND(50.8,3),ROUND(E24,3)=ROUND(0,3),ROUND(F24,3)=ROUND(50.8,3)),"✓","✗"))</f>
+        <f aca="false">IF(COUNT(B24:F24)=0,"",IF(AND(ROUND(B24,3)=ROUND(6.4,3),ROUND(C24,3)=ROUND(11,3),ROUND(D24,3)=ROUND(53.2,3),ROUND(E24,3)=ROUND(0,3),ROUND(F24,3)=ROUND(53.2,3)),"✓","✗"))</f>
         <v/>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C26" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="D26" s="11"/>
+      <c r="D26" s="11" t="s">
+        <v>54</v>
+      </c>
       <c r="E26" s="11"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="5" t="str">
-        <f aca="false">IF(F26="","",IF(ROUND(F26,3)=ROUND(2.5,3),"✓","✗"))</f>
+      <c r="F26" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G26" s="12"/>
+      <c r="H26" s="5" t="str">
+        <f aca="false">IF(G26="","",IF(ROUND(G26,3)=ROUND(2.5,3),"✓","✗"))</f>
         <v/>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C28" s="11"/>
+        <v>55</v>
+      </c>
       <c r="D28" s="11"/>
       <c r="E28" s="11"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="5" t="str">
-        <f aca="false">IF(F28="","",IF(ROUND(F28,3)=ROUND(2.5,3),"✓","✗"))</f>
+      <c r="F28" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G28" s="12"/>
+      <c r="H28" s="5" t="str">
+        <f aca="false">IF(G28="","",IF(ROUND(G28,3)=ROUND(2.5,3),"✓","✗"))</f>
         <v/>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C30" s="11"/>
+        <v>56</v>
+      </c>
       <c r="D30" s="11"/>
       <c r="E30" s="11"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="5" t="str">
-        <f aca="false">IF(F30="","",IF(ROUND(F30,3)=ROUND(9.5,3),"✓","✗"))</f>
+      <c r="F30" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G30" s="12"/>
+      <c r="H30" s="5" t="str">
+        <f aca="false">IF(G30="","",IF(ROUND(G30,3)=ROUND(9.5,3),"✓","✗"))</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="D30:E30"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:J30">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
@@ -1519,7 +1530,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -1530,192 +1541,208 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C9" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="D9" s="11"/>
+      <c r="D9" s="11" t="s">
+        <v>62</v>
+      </c>
       <c r="E9" s="11"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="5" t="str">
-        <f aca="false">IF(F9="","",IF(ROUND(F9,3)=ROUND(0.46875,3),"✓","✗"))</f>
+      <c r="F9" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9" s="12"/>
+      <c r="H9" s="5" t="str">
+        <f aca="false">IF(G9="","",IF(ROUND(G9,3)=ROUND(0.46875,3),"✓","✗"))</f>
         <v/>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C17" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="D17" s="11"/>
+      <c r="D17" s="11" t="s">
+        <v>74</v>
+      </c>
       <c r="E17" s="11"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="5" t="str">
-        <f aca="false">IF(F17="","",IF(ROUND(F17,3)=ROUND(0,3),"✓","✗"))</f>
+      <c r="F17" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G17" s="12"/>
+      <c r="H17" s="5" t="str">
+        <f aca="false">IF(G17="","",IF(ROUND(G17,3)=ROUND(0,3),"✓","✗"))</f>
         <v/>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="C19" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="D19" s="11"/>
+      <c r="D19" s="11" t="s">
+        <v>76</v>
+      </c>
       <c r="E19" s="11"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="5" t="str">
-        <f aca="false">IF(F19="","",IF(ROUND(F19,3)=ROUND(0.375,3),"✓","✗"))</f>
+      <c r="F19" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G19" s="12"/>
+      <c r="H19" s="5" t="str">
+        <f aca="false">IF(G19="","",IF(ROUND(G19,3)=ROUND(0.375,3),"✓","✗"))</f>
         <v/>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C21" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="D21" s="11"/>
+      <c r="D21" s="11" t="s">
+        <v>78</v>
+      </c>
       <c r="E21" s="11"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="5" t="str">
-        <f aca="false">IF(F21="","",IF(ROUND(F21,3)=ROUND(0.1875,3),"✓","✗"))</f>
+      <c r="F21" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G21" s="12"/>
+      <c r="H21" s="5" t="str">
+        <f aca="false">IF(G21="","",IF(ROUND(G21,3)=ROUND(0.1875,3),"✓","✗"))</f>
         <v/>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C23" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="D23" s="11"/>
+      <c r="D23" s="11" t="s">
+        <v>80</v>
+      </c>
       <c r="E23" s="11"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="5" t="str">
-        <f aca="false">IF(F23="","",IF(ROUND(F23,3)=ROUND(0.48,3),"✓","✗"))</f>
+      <c r="F23" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G23" s="12"/>
+      <c r="H23" s="5" t="str">
+        <f aca="false">IF(G23="","",IF(ROUND(G23,3)=ROUND(0.48,3),"✓","✗"))</f>
         <v/>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="C25" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="D25" s="11"/>
+      <c r="D25" s="11" t="s">
+        <v>82</v>
+      </c>
       <c r="E25" s="11"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="5" t="str">
-        <f aca="false">IF(F25="","",IF(ROUND(F25,3)=ROUND(0.444444,3),"✓","✗"))</f>
+      <c r="F25" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G25" s="12"/>
+      <c r="H25" s="5" t="str">
+        <f aca="false">IF(G25="","",IF(ROUND(G25,3)=ROUND(0.444444,3),"✓","✗"))</f>
         <v/>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="C27" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="D27" s="11"/>
+      <c r="D27" s="11" t="s">
+        <v>84</v>
+      </c>
       <c r="E27" s="11"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="5" t="str">
-        <f aca="false">IF(F27="","",IF(ROUND(F27,3)=ROUND(0.466667,3),"✓","✗"))</f>
+      <c r="F27" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G27" s="12"/>
+      <c r="H27" s="5" t="str">
+        <f aca="false">IF(G27="","",IF(ROUND(G27,3)=ROUND(0.466667,3),"✓","✗"))</f>
         <v/>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="C29" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="D29" s="11"/>
+      <c r="D29" s="11" t="s">
+        <v>86</v>
+      </c>
       <c r="E29" s="11"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="5" t="str">
-        <f aca="false">IF(F29="","",IF(UPPER(TRIM(F29))=UPPER("A"),"✓","✗"))</f>
+      <c r="F29" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G29" s="12"/>
+      <c r="H29" s="5" t="str">
+        <f aca="false">IF(G29="","",IF(UPPER(TRIM(G29))=UPPER("A"),"✓","✗"))</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="C27:E27"/>
-    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="D29:E29"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:J29">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
@@ -1740,7 +1767,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -1751,39 +1778,39 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F9" s="10" t="s">
         <v>36</v>
@@ -1791,7 +1818,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B10" s="7" t="n">
         <v>4</v>
@@ -1810,7 +1837,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B11" s="7" t="n">
         <v>9</v>
@@ -1829,91 +1856,101 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="C15" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="D15" s="11"/>
+      <c r="D15" s="11" t="s">
+        <v>100</v>
+      </c>
       <c r="E15" s="11"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="5" t="str">
-        <f aca="false">IF(F15="","",IF(ROUND(F15,3)=ROUND(10,3),"✓","✗"))</f>
+      <c r="F15" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G15" s="12"/>
+      <c r="H15" s="5" t="str">
+        <f aca="false">IF(G15="","",IF(ROUND(G15,3)=ROUND(10,3),"✓","✗"))</f>
         <v/>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="C17" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="D17" s="11"/>
+      <c r="D17" s="11" t="s">
+        <v>102</v>
+      </c>
       <c r="E17" s="11"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="5" t="str">
-        <f aca="false">IF(F17="","",IF(ROUND(F17,3)=ROUND(1,3),"✓","✗"))</f>
+      <c r="F17" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G17" s="12"/>
+      <c r="H17" s="5" t="str">
+        <f aca="false">IF(G17="","",IF(ROUND(G17,3)=ROUND(1,3),"✓","✗"))</f>
         <v/>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="C19" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="D19" s="11"/>
+      <c r="D19" s="11" t="s">
+        <v>104</v>
+      </c>
       <c r="E19" s="11"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="5" t="str">
-        <f aca="false">IF(F19="","",IF(ROUND(F19,3)=ROUND(9,3),"✓","✗"))</f>
+      <c r="F19" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G19" s="12"/>
+      <c r="H19" s="5" t="str">
+        <f aca="false">IF(G19="","",IF(ROUND(G19,3)=ROUND(9,3),"✓","✗"))</f>
         <v/>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="C21" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="D21" s="11"/>
+      <c r="D21" s="11" t="s">
+        <v>106</v>
+      </c>
       <c r="E21" s="11"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="5" t="str">
-        <f aca="false">IF(F21="","",IF(ROUND(F21,3)=ROUND(1.9,3),"✓","✗"))</f>
+      <c r="F21" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G21" s="12"/>
+      <c r="H21" s="5" t="str">
+        <f aca="false">IF(G21="","",IF(ROUND(G21,3)=ROUND(1.9,3),"✓","✗"))</f>
         <v/>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="C23" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="D23" s="11"/>
+      <c r="D23" s="11" t="s">
+        <v>108</v>
+      </c>
       <c r="E23" s="11"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="5" t="str">
-        <f aca="false">IF(F23="","",IF(ROUND(F23,3)=ROUND(22,3),"✓","✗"))</f>
+      <c r="F23" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G23" s="12"/>
+      <c r="H23" s="5" t="str">
+        <f aca="false">IF(G23="","",IF(ROUND(G23,3)=ROUND(22,3),"✓","✗"))</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="D23:E23"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:J23">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
@@ -1947,30 +1984,30 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B8" s="7" t="n">
         <v>14</v>
@@ -1978,41 +2015,41 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B18" s="7" t="n">
         <v>0.4688</v>
@@ -2020,7 +2057,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B19" s="7" t="n">
         <v>0.1875</v>
@@ -2028,7 +2065,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B20" s="7" t="n">
         <v>0.4667</v>
@@ -2036,39 +2073,39 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
